--- a/artfynd/A 34759-2026 artfynd.xlsx
+++ b/artfynd/A 34759-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136406088</v>
       </c>
       <c r="B2" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136405901</v>
       </c>
       <c r="B3" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136405504</v>
       </c>
       <c r="B4" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>136405643</v>
       </c>
       <c r="B25" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>136405659</v>
       </c>
       <c r="B26" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>136405681</v>
       </c>
       <c r="B27" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 34759-2026 artfynd.xlsx
+++ b/artfynd/A 34759-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136406088</v>
       </c>
       <c r="B2" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136405901</v>
       </c>
       <c r="B3" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136405504</v>
       </c>
       <c r="B4" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>136405643</v>
       </c>
       <c r="B25" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>136405659</v>
       </c>
       <c r="B26" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>136405681</v>
       </c>
       <c r="B27" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 34759-2026 artfynd.xlsx
+++ b/artfynd/A 34759-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136406088</v>
       </c>
       <c r="B2" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136405901</v>
       </c>
       <c r="B3" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136405504</v>
       </c>
       <c r="B4" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>136405517</v>
       </c>
       <c r="B5" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136405541</v>
       </c>
       <c r="B6" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>136405565</v>
       </c>
       <c r="B7" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>136405580</v>
       </c>
       <c r="B8" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>136405595</v>
       </c>
       <c r="B9" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>136405632</v>
       </c>
       <c r="B10" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>136405639</v>
       </c>
       <c r="B11" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>136405667</v>
       </c>
       <c r="B12" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>136405694</v>
       </c>
       <c r="B13" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>136405713</v>
       </c>
       <c r="B14" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>136405837</v>
       </c>
       <c r="B15" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>136405856</v>
       </c>
       <c r="B16" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>136405858</v>
       </c>
       <c r="B17" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>136405655</v>
       </c>
       <c r="B18" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>136405807</v>
       </c>
       <c r="B19" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>136405900</v>
       </c>
       <c r="B20" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>136405773</v>
       </c>
       <c r="B21" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>136405793</v>
       </c>
       <c r="B22" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>136405799</v>
       </c>
       <c r="B23" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>136406186</v>
       </c>
       <c r="B24" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>136405643</v>
       </c>
       <c r="B25" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>136405659</v>
       </c>
       <c r="B26" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>136405681</v>
       </c>
       <c r="B27" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
